--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N78_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N78_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.65978397071741</v>
+        <v>5.144714895241578</v>
       </c>
       <c r="D2" t="n">
-        <v>31.59044558345607</v>
+        <v>5.133447407311611</v>
       </c>
       <c r="E2" t="n">
-        <v>11.4545264671241</v>
+        <v>1.861360550907666</v>
       </c>
       <c r="F2" t="n">
-        <v>11.65104457261592</v>
+        <v>1.893294743050088</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.5688369049656</v>
+        <v>8.86743599705691</v>
       </c>
       <c r="D3" t="n">
-        <v>54.89253472868791</v>
+        <v>8.920036893411787</v>
       </c>
       <c r="E3" t="n">
-        <v>11.4545264671241</v>
+        <v>1.861360550907666</v>
       </c>
       <c r="F3" t="n">
-        <v>11.65104457261592</v>
+        <v>1.893294743050088</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
